--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.42680636849305</v>
+        <v>10.95685603488012</v>
       </c>
       <c r="D2" t="n">
-        <v>34.91776052383658</v>
+        <v>5.674136085123444</v>
       </c>
       <c r="E2" t="n">
-        <v>27.6983311227528</v>
+        <v>4.50097880744733</v>
       </c>
       <c r="F2" t="n">
-        <v>12.62079508764897</v>
+        <v>2.050879201742958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.82695378486526</v>
+        <v>2.571879990040605</v>
       </c>
       <c r="D3" t="n">
-        <v>16.70282196461887</v>
+        <v>2.714208569250566</v>
       </c>
       <c r="E3" t="n">
-        <v>27.6983311227528</v>
+        <v>4.50097880744733</v>
       </c>
       <c r="F3" t="n">
-        <v>12.62079508764897</v>
+        <v>2.050879201742958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.476121611789294</v>
+        <v>0.5648697619157603</v>
       </c>
       <c r="D4" t="n">
-        <v>4.178321411065213</v>
+        <v>0.6789772292980972</v>
       </c>
       <c r="E4" t="n">
-        <v>27.6983311227528</v>
+        <v>4.50097880744733</v>
       </c>
       <c r="F4" t="n">
-        <v>12.62079508764897</v>
+        <v>2.050879201742958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
